--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5B0B46-792A-F14C-9A9A-14721BEAAA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E1CFE5-FAAA-DB48-A5F6-90FC867CC6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="12760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="294">
   <si>
     <t>category</t>
   </si>
@@ -796,9 +796,6 @@
     <t>Q000</t>
   </si>
   <si>
-    <t>TBD - Cat G</t>
-  </si>
-  <si>
     <t>TBD - Cat H</t>
   </si>
   <si>
@@ -899,6 +896,12 @@
   </si>
   <si>
     <t>categoryT</t>
+  </si>
+  <si>
+    <t>Shri Rama</t>
+  </si>
+  <si>
+    <t>G001</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q181"/>
+  <dimension ref="A1:Q182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1300,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1341,7 +1344,7 @@
         <v>216</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -1368,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>25</v>
@@ -1409,7 +1412,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
@@ -1444,7 +1447,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1479,7 +1482,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -1514,7 +1517,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1549,7 +1552,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -1584,7 +1587,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -1619,7 +1622,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1654,7 +1657,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1689,7 +1692,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1724,7 +1727,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -1759,7 +1762,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -1794,7 +1797,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -1829,7 +1832,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -1864,7 +1867,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -1899,7 +1902,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
@@ -1934,7 +1937,7 @@
         <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
         <v>61</v>
@@ -1969,7 +1972,7 @@
         <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -2004,7 +2007,7 @@
         <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E21" t="s">
         <v>65</v>
@@ -2039,7 +2042,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -2074,7 +2077,7 @@
         <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>25</v>
@@ -2115,7 +2118,7 @@
         <v>72</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E24" t="s">
         <v>26</v>
@@ -2150,7 +2153,7 @@
         <v>73</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -2185,7 +2188,7 @@
         <v>74</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -2220,7 +2223,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
@@ -2255,7 +2258,7 @@
         <v>76</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
         <v>56</v>
@@ -2290,7 +2293,7 @@
         <v>77</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
@@ -2325,7 +2328,7 @@
         <v>78</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s">
         <v>31</v>
@@ -2360,7 +2363,7 @@
         <v>79</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E31" t="s">
         <v>32</v>
@@ -2395,7 +2398,7 @@
         <v>80</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E32" t="s">
         <v>33</v>
@@ -2430,7 +2433,7 @@
         <v>81</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E33" t="s">
         <v>34</v>
@@ -2465,7 +2468,7 @@
         <v>82</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E34" t="s">
         <v>35</v>
@@ -2500,7 +2503,7 @@
         <v>83</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s">
         <v>36</v>
@@ -2535,7 +2538,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E36" t="s">
         <v>37</v>
@@ -2570,7 +2573,7 @@
         <v>85</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -2605,7 +2608,7 @@
         <v>86</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E38" t="s">
         <v>39</v>
@@ -2640,7 +2643,7 @@
         <v>87</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E39" t="s">
         <v>61</v>
@@ -2675,7 +2678,7 @@
         <v>88</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E40" t="s">
         <v>63</v>
@@ -2710,7 +2713,7 @@
         <v>89</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E41" t="s">
         <v>65</v>
@@ -2745,7 +2748,7 @@
         <v>90</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E42" t="s">
         <v>67</v>
@@ -2780,7 +2783,7 @@
         <v>217</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -2807,7 +2810,7 @@
         <v>94</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>25</v>
@@ -2848,7 +2851,7 @@
         <v>95</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
@@ -2883,7 +2886,7 @@
         <v>96</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2918,7 +2921,7 @@
         <v>97</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -2953,7 +2956,7 @@
         <v>98</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E48" t="s">
         <v>29</v>
@@ -2988,7 +2991,7 @@
         <v>99</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E49" t="s">
         <v>56</v>
@@ -3023,7 +3026,7 @@
         <v>100</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -3058,7 +3061,7 @@
         <v>101</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
@@ -3093,7 +3096,7 @@
         <v>102</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E52" t="s">
         <v>32</v>
@@ -3128,7 +3131,7 @@
         <v>103</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -3163,7 +3166,7 @@
         <v>104</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E54" t="s">
         <v>34</v>
@@ -3198,7 +3201,7 @@
         <v>105</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E55" t="s">
         <v>35</v>
@@ -3233,7 +3236,7 @@
         <v>106</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
@@ -3268,7 +3271,7 @@
         <v>107</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E57" t="s">
         <v>37</v>
@@ -3303,7 +3306,7 @@
         <v>108</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E58" t="s">
         <v>38</v>
@@ -3338,7 +3341,7 @@
         <v>109</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E59" t="s">
         <v>39</v>
@@ -3373,7 +3376,7 @@
         <v>110</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E60" t="s">
         <v>61</v>
@@ -3408,7 +3411,7 @@
         <v>111</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E61" t="s">
         <v>63</v>
@@ -3443,7 +3446,7 @@
         <v>112</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E62" t="s">
         <v>65</v>
@@ -3478,7 +3481,7 @@
         <v>113</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E63" t="s">
         <v>67</v>
@@ -3513,7 +3516,7 @@
         <v>114</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>25</v>
@@ -3554,7 +3557,7 @@
         <v>115</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E65" t="s">
         <v>26</v>
@@ -3589,7 +3592,7 @@
         <v>116</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
@@ -3624,7 +3627,7 @@
         <v>117</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -3659,7 +3662,7 @@
         <v>118</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E68" t="s">
         <v>29</v>
@@ -3694,7 +3697,7 @@
         <v>119</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
@@ -3729,7 +3732,7 @@
         <v>120</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E70" t="s">
         <v>30</v>
@@ -3764,7 +3767,7 @@
         <v>121</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E71" t="s">
         <v>31</v>
@@ -3799,7 +3802,7 @@
         <v>122</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E72" t="s">
         <v>32</v>
@@ -3834,7 +3837,7 @@
         <v>123</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E73" t="s">
         <v>33</v>
@@ -3869,7 +3872,7 @@
         <v>124</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E74" t="s">
         <v>34</v>
@@ -3904,7 +3907,7 @@
         <v>125</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E75" t="s">
         <v>35</v>
@@ -3939,7 +3942,7 @@
         <v>126</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E76" t="s">
         <v>36</v>
@@ -3974,7 +3977,7 @@
         <v>127</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E77" t="s">
         <v>37</v>
@@ -4009,7 +4012,7 @@
         <v>128</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E78" t="s">
         <v>38</v>
@@ -4044,7 +4047,7 @@
         <v>129</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E79" t="s">
         <v>39</v>
@@ -4079,7 +4082,7 @@
         <v>130</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E80" t="s">
         <v>61</v>
@@ -4114,7 +4117,7 @@
         <v>131</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E81" t="s">
         <v>63</v>
@@ -4149,7 +4152,7 @@
         <v>132</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E82" t="s">
         <v>65</v>
@@ -4184,7 +4187,7 @@
         <v>133</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E83" t="s">
         <v>67</v>
@@ -4219,7 +4222,7 @@
         <v>220</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>221</v>
@@ -4262,7 +4265,7 @@
         <v>134</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>25</v>
@@ -4303,7 +4306,7 @@
         <v>135</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E86" t="s">
         <v>26</v>
@@ -4338,7 +4341,7 @@
         <v>136</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E87" t="s">
         <v>27</v>
@@ -4373,7 +4376,7 @@
         <v>137</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -4408,7 +4411,7 @@
         <v>138</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E89" t="s">
         <v>29</v>
@@ -4443,7 +4446,7 @@
         <v>139</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E90" t="s">
         <v>56</v>
@@ -4478,7 +4481,7 @@
         <v>140</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E91" t="s">
         <v>30</v>
@@ -4513,7 +4516,7 @@
         <v>141</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E92" t="s">
         <v>31</v>
@@ -4548,7 +4551,7 @@
         <v>142</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E93" t="s">
         <v>32</v>
@@ -4583,7 +4586,7 @@
         <v>143</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E94" t="s">
         <v>33</v>
@@ -4618,7 +4621,7 @@
         <v>144</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E95" t="s">
         <v>34</v>
@@ -4653,7 +4656,7 @@
         <v>145</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E96" t="s">
         <v>35</v>
@@ -4688,7 +4691,7 @@
         <v>146</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E97" t="s">
         <v>36</v>
@@ -4723,7 +4726,7 @@
         <v>147</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E98" t="s">
         <v>37</v>
@@ -4758,7 +4761,7 @@
         <v>148</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E99" t="s">
         <v>38</v>
@@ -4793,7 +4796,7 @@
         <v>149</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E100" t="s">
         <v>39</v>
@@ -4828,7 +4831,7 @@
         <v>150</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
@@ -4863,7 +4866,7 @@
         <v>151</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E102" t="s">
         <v>63</v>
@@ -4898,7 +4901,7 @@
         <v>152</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E103" t="s">
         <v>65</v>
@@ -4933,7 +4936,7 @@
         <v>153</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E104" t="s">
         <v>67</v>
@@ -4968,7 +4971,7 @@
         <v>154</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>25</v>
@@ -5009,7 +5012,7 @@
         <v>155</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E106" t="s">
         <v>26</v>
@@ -5044,7 +5047,7 @@
         <v>156</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E107" t="s">
         <v>27</v>
@@ -5079,7 +5082,7 @@
         <v>157</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5114,7 +5117,7 @@
         <v>158</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E109" t="s">
         <v>29</v>
@@ -5149,7 +5152,7 @@
         <v>159</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E110" t="s">
         <v>56</v>
@@ -5184,7 +5187,7 @@
         <v>160</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E111" t="s">
         <v>30</v>
@@ -5219,7 +5222,7 @@
         <v>161</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E112" t="s">
         <v>31</v>
@@ -5254,7 +5257,7 @@
         <v>162</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E113" t="s">
         <v>32</v>
@@ -5289,7 +5292,7 @@
         <v>163</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E114" t="s">
         <v>33</v>
@@ -5324,7 +5327,7 @@
         <v>164</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E115" t="s">
         <v>34</v>
@@ -5359,7 +5362,7 @@
         <v>165</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E116" t="s">
         <v>35</v>
@@ -5394,7 +5397,7 @@
         <v>166</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E117" t="s">
         <v>36</v>
@@ -5429,7 +5432,7 @@
         <v>167</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E118" t="s">
         <v>37</v>
@@ -5464,7 +5467,7 @@
         <v>168</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E119" t="s">
         <v>38</v>
@@ -5499,7 +5502,7 @@
         <v>169</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E120" t="s">
         <v>39</v>
@@ -5534,7 +5537,7 @@
         <v>170</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E121" t="s">
         <v>61</v>
@@ -5569,7 +5572,7 @@
         <v>171</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E122" t="s">
         <v>63</v>
@@ -5604,7 +5607,7 @@
         <v>172</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E123" t="s">
         <v>65</v>
@@ -5639,7 +5642,7 @@
         <v>173</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E124" t="s">
         <v>67</v>
@@ -5674,7 +5677,7 @@
         <v>223</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>221</v>
@@ -5717,7 +5720,7 @@
         <v>174</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>25</v>
@@ -5758,7 +5761,7 @@
         <v>175</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E127" t="s">
         <v>26</v>
@@ -5793,7 +5796,7 @@
         <v>176</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E128" t="s">
         <v>27</v>
@@ -5828,7 +5831,7 @@
         <v>177</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -5863,7 +5866,7 @@
         <v>178</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E130" t="s">
         <v>29</v>
@@ -5898,7 +5901,7 @@
         <v>179</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E131" t="s">
         <v>56</v>
@@ -5933,7 +5936,7 @@
         <v>180</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E132" t="s">
         <v>30</v>
@@ -5968,7 +5971,7 @@
         <v>181</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E133" t="s">
         <v>31</v>
@@ -6003,7 +6006,7 @@
         <v>182</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E134" t="s">
         <v>32</v>
@@ -6038,7 +6041,7 @@
         <v>183</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E135" t="s">
         <v>33</v>
@@ -6073,7 +6076,7 @@
         <v>184</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E136" t="s">
         <v>34</v>
@@ -6108,7 +6111,7 @@
         <v>185</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E137" t="s">
         <v>35</v>
@@ -6143,7 +6146,7 @@
         <v>186</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E138" t="s">
         <v>36</v>
@@ -6178,7 +6181,7 @@
         <v>187</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E139" t="s">
         <v>37</v>
@@ -6213,7 +6216,7 @@
         <v>188</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E140" t="s">
         <v>38</v>
@@ -6248,7 +6251,7 @@
         <v>189</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E141" t="s">
         <v>39</v>
@@ -6283,7 +6286,7 @@
         <v>190</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E142" t="s">
         <v>61</v>
@@ -6318,7 +6321,7 @@
         <v>191</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
         <v>63</v>
@@ -6353,7 +6356,7 @@
         <v>192</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
@@ -6388,7 +6391,7 @@
         <v>193</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E145" t="s">
         <v>67</v>
@@ -6423,7 +6426,7 @@
         <v>194</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>25</v>
@@ -6464,7 +6467,7 @@
         <v>195</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E147" t="s">
         <v>26</v>
@@ -6499,7 +6502,7 @@
         <v>196</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E148" t="s">
         <v>27</v>
@@ -6534,7 +6537,7 @@
         <v>197</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6569,7 +6572,7 @@
         <v>198</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E150" t="s">
         <v>29</v>
@@ -6604,7 +6607,7 @@
         <v>199</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E151" t="s">
         <v>56</v>
@@ -6639,7 +6642,7 @@
         <v>200</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E152" t="s">
         <v>30</v>
@@ -6674,7 +6677,7 @@
         <v>201</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E153" t="s">
         <v>31</v>
@@ -6709,7 +6712,7 @@
         <v>202</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E154" t="s">
         <v>32</v>
@@ -6744,7 +6747,7 @@
         <v>203</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E155" t="s">
         <v>33</v>
@@ -6779,7 +6782,7 @@
         <v>204</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E156" t="s">
         <v>34</v>
@@ -6814,7 +6817,7 @@
         <v>205</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E157" t="s">
         <v>35</v>
@@ -6849,7 +6852,7 @@
         <v>206</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E158" t="s">
         <v>36</v>
@@ -6884,7 +6887,7 @@
         <v>207</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E159" t="s">
         <v>37</v>
@@ -6919,7 +6922,7 @@
         <v>208</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E160" t="s">
         <v>38</v>
@@ -6954,7 +6957,7 @@
         <v>209</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E161" t="s">
         <v>39</v>
@@ -6989,7 +6992,7 @@
         <v>210</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E162" t="s">
         <v>61</v>
@@ -7024,7 +7027,7 @@
         <v>211</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E163" t="s">
         <v>63</v>
@@ -7059,7 +7062,7 @@
         <v>212</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E164" t="s">
         <v>65</v>
@@ -7094,7 +7097,7 @@
         <v>213</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E165" t="s">
         <v>67</v>
@@ -7129,7 +7132,7 @@
         <v>224</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E166" t="s">
         <v>221</v>
@@ -7164,7 +7167,7 @@
         <v>228</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E167" t="s">
         <v>221</v>
@@ -7193,13 +7196,13 @@
         <v>230</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E168" t="s">
         <v>221</v>
@@ -7225,51 +7228,51 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E169" t="s">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="F169" t="s">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="G169" t="s">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="H169" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J169" t="s">
-        <v>221</v>
-      </c>
-      <c r="K169" t="s">
-        <v>221</v>
+        <v>70</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E170" t="s">
         <v>221</v>
@@ -7295,16 +7298,16 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E171" t="s">
         <v>221</v>
@@ -7330,16 +7333,16 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E172" t="s">
         <v>221</v>
@@ -7365,16 +7368,16 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E173" t="s">
         <v>221</v>
@@ -7400,16 +7403,16 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E174" t="s">
         <v>221</v>
@@ -7435,16 +7438,16 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E175" t="s">
         <v>221</v>
@@ -7470,16 +7473,16 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E176" t="s">
         <v>221</v>
@@ -7505,16 +7508,16 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E177" t="s">
         <v>221</v>
@@ -7540,16 +7543,16 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E178" t="s">
         <v>221</v>
@@ -7575,16 +7578,16 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E179" t="s">
         <v>221</v>
@@ -7610,16 +7613,16 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E180" t="s">
         <v>221</v>
@@ -7645,36 +7648,71 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E181" t="s">
+        <v>221</v>
+      </c>
+      <c r="F181" t="s">
+        <v>221</v>
+      </c>
+      <c r="G181" t="s">
+        <v>221</v>
+      </c>
+      <c r="H181" t="s">
+        <v>221</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J181" t="s">
+        <v>221</v>
+      </c>
+      <c r="K181" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A182" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C181" s="2" t="s">
+      <c r="B182" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D181" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E181" t="s">
-        <v>221</v>
-      </c>
-      <c r="F181" t="s">
-        <v>221</v>
-      </c>
-      <c r="G181" t="s">
-        <v>221</v>
-      </c>
-      <c r="H181" t="s">
-        <v>221</v>
-      </c>
-      <c r="I181" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J181" t="s">
-        <v>221</v>
-      </c>
-      <c r="K181" t="s">
+      <c r="D182" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E182" t="s">
+        <v>221</v>
+      </c>
+      <c r="F182" t="s">
+        <v>221</v>
+      </c>
+      <c r="G182" t="s">
+        <v>221</v>
+      </c>
+      <c r="H182" t="s">
+        <v>221</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J182" t="s">
+        <v>221</v>
+      </c>
+      <c r="K182" t="s">
         <v>221</v>
       </c>
     </row>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/Already backed up sangrahaalaya on 08182026 9.30 pm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6445D88F-C36F-E543-8C2A-0B6C6ADB4D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB7B777-2D5B-674E-8686-7BC6ACA4DD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="213">
   <si>
     <t>category</t>
   </si>
@@ -442,9 +442,6 @@
     <t>TBD - Cat N</t>
   </si>
   <si>
-    <t>TBD - Cat O</t>
-  </si>
-  <si>
     <t>TBD - Cat P</t>
   </si>
   <si>
@@ -526,9 +523,6 @@
     <t>Shri Rama</t>
   </si>
   <si>
-    <t>G001</t>
-  </si>
-  <si>
     <t>Shri_Ganesha_Ashtottaram</t>
   </si>
   <si>
@@ -626,6 +620,45 @@
   </si>
   <si>
     <t>Durga_saptashathi.pdf</t>
+  </si>
+  <si>
+    <t>TBD - Cat G</t>
+  </si>
+  <si>
+    <t>O001</t>
+  </si>
+  <si>
+    <t>Rama_chaalisa</t>
+  </si>
+  <si>
+    <t>Rama_chaalisa.pdf</t>
+  </si>
+  <si>
+    <t>Shri_rama_aapaduddhaaraka_stotram</t>
+  </si>
+  <si>
+    <t>Shri_rama_aapaduddhaaraka_stotram.pdf</t>
+  </si>
+  <si>
+    <t>O002</t>
+  </si>
+  <si>
+    <t>O003</t>
+  </si>
+  <si>
+    <t>O004</t>
+  </si>
+  <si>
+    <t>Shri_rama_durga_stotram</t>
+  </si>
+  <si>
+    <t>Shri_rama_durga_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_rama_rakshaa_stotram</t>
+  </si>
+  <si>
+    <t>Shri_rama_rakshaa_stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1027,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1068,7 +1101,7 @@
         <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -1095,7 +1128,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>25</v>
@@ -1136,7 +1169,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
@@ -1171,7 +1204,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1206,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -1241,7 +1274,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1276,7 +1309,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -1311,7 +1344,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -1346,7 +1379,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1381,7 +1414,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1416,7 +1449,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1451,7 +1484,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -1486,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -1521,7 +1554,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -1556,7 +1589,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -1591,7 +1624,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -1626,7 +1659,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
@@ -1661,7 +1694,7 @@
         <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>61</v>
@@ -1696,7 +1729,7 @@
         <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -1731,7 +1764,7 @@
         <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>65</v>
@@ -1766,7 +1799,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -1801,7 +1834,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1828,19 +1861,19 @@
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>70</v>
@@ -1869,19 +1902,19 @@
         <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>70</v>
@@ -1904,19 +1937,19 @@
         <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>70</v>
@@ -1939,19 +1972,19 @@
         <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>70</v>
@@ -1974,19 +2007,19 @@
         <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>70</v>
@@ -2009,7 +2042,7 @@
         <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>97</v>
@@ -2052,19 +2085,19 @@
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>70</v>
@@ -2093,19 +2126,19 @@
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H31" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>70</v>
@@ -2128,19 +2161,19 @@
         <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H32" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>70</v>
@@ -2163,19 +2196,19 @@
         <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H33" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>70</v>
@@ -2198,19 +2231,19 @@
         <v>83</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H34" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>70</v>
@@ -2233,19 +2266,19 @@
         <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H35" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>70</v>
@@ -2268,19 +2301,19 @@
         <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>70</v>
@@ -2303,19 +2336,19 @@
         <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H37" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>70</v>
@@ -2338,19 +2371,19 @@
         <v>87</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H38" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>70</v>
@@ -2373,19 +2406,19 @@
         <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>70</v>
@@ -2402,13 +2435,13 @@
         <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>97</v>
@@ -2445,25 +2478,25 @@
         <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>70</v>
@@ -2492,7 +2525,7 @@
         <v>99</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -2527,7 +2560,7 @@
         <v>103</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E43" t="s">
         <v>97</v>
@@ -2556,13 +2589,13 @@
         <v>105</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E44" t="s">
         <v>97</v>
@@ -2588,48 +2621,48 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>153</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="G45" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="H45" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
-      </c>
-      <c r="K45">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J45" t="s">
+        <v>97</v>
+      </c>
+      <c r="K45" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>154</v>
@@ -2658,13 +2691,13 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>155</v>
@@ -2693,13 +2726,13 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>156</v>
@@ -2728,13 +2761,13 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>157</v>
@@ -2763,13 +2796,13 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>158</v>
@@ -2798,13 +2831,13 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>159</v>
@@ -2833,13 +2866,13 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>160</v>
@@ -2871,153 +2904,153 @@
         <v>113</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="H53" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J53" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="H54" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J54" t="s">
-        <v>97</v>
-      </c>
-      <c r="K54" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54">
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E55" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="F55" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="G55" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H55" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K55" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J55">
+        <v>3</v>
+      </c>
+      <c r="K55">
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="F56" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="H56" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" t="s">
-        <v>97</v>
-      </c>
-      <c r="K56" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
+      <c r="K56">
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
         <v>97</v>
@@ -3043,36 +3076,141 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" t="s">
+        <v>97</v>
+      </c>
+      <c r="F58" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" t="s">
+        <v>97</v>
+      </c>
+      <c r="H58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J58" t="s">
+        <v>97</v>
+      </c>
+      <c r="K58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" t="s">
+        <v>97</v>
+      </c>
+      <c r="F59" t="s">
+        <v>97</v>
+      </c>
+      <c r="G59" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" t="s">
+        <v>97</v>
+      </c>
+      <c r="K59" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F60" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" t="s">
+        <v>97</v>
+      </c>
+      <c r="H60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J60" t="s">
+        <v>97</v>
+      </c>
+      <c r="K60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="B61" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E58" t="s">
-        <v>97</v>
-      </c>
-      <c r="F58" t="s">
-        <v>97</v>
-      </c>
-      <c r="G58" t="s">
-        <v>97</v>
-      </c>
-      <c r="H58" t="s">
-        <v>97</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J58" t="s">
-        <v>97</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="D61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" t="s">
+        <v>97</v>
+      </c>
+      <c r="K61" t="s">
         <v>97</v>
       </c>
     </row>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/Already backed up sangrahaalaya on 08182026 9.30 pm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB7B777-2D5B-674E-8686-7BC6ACA4DD8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6CB773-7E5E-4447-8173-84738E218847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="216">
   <si>
     <t>category</t>
   </si>
@@ -424,9 +424,6 @@
     <t>TBD - Cat H</t>
   </si>
   <si>
-    <t>TBD - Cat I</t>
-  </si>
-  <si>
     <t>TBD - Cat J</t>
   </si>
   <si>
@@ -613,9 +610,6 @@
     <t>Lakshmi_ashtottara_shata_nama_stotram.pdf</t>
   </si>
   <si>
-    <t>Paaraayanam</t>
-  </si>
-  <si>
     <t>Durga_saptashathi</t>
   </si>
   <si>
@@ -659,6 +653,21 @@
   </si>
   <si>
     <t>Shri_rama_rakshaa_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri Durga</t>
+  </si>
+  <si>
+    <t>I001</t>
+  </si>
+  <si>
+    <t>Festivals</t>
+  </si>
+  <si>
+    <t>Yajur_upaakarma</t>
+  </si>
+  <si>
+    <t>Yajur_upaakarma.pdf</t>
   </si>
 </sst>
 </file>
@@ -1030,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1060,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1101,7 +1110,7 @@
         <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -1128,7 +1137,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>25</v>
@@ -1169,7 +1178,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
@@ -1204,7 +1213,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1239,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -1274,7 +1283,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1309,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -1344,7 +1353,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -1379,7 +1388,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1414,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1449,7 +1458,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1484,7 +1493,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -1519,7 +1528,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -1554,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -1589,7 +1598,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -1624,7 +1633,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -1659,7 +1668,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
@@ -1694,7 +1703,7 @@
         <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>61</v>
@@ -1729,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -1764,7 +1773,7 @@
         <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E21" t="s">
         <v>65</v>
@@ -1799,7 +1808,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -1834,7 +1843,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1861,19 +1870,19 @@
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>70</v>
@@ -1902,19 +1911,19 @@
         <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" t="s">
         <v>168</v>
-      </c>
-      <c r="F25" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" t="s">
-        <v>168</v>
-      </c>
-      <c r="H25" t="s">
-        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>70</v>
@@ -1937,19 +1946,19 @@
         <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" t="s">
+        <v>170</v>
+      </c>
+      <c r="G26" t="s">
+        <v>170</v>
+      </c>
+      <c r="H26" t="s">
         <v>171</v>
-      </c>
-      <c r="F26" t="s">
-        <v>171</v>
-      </c>
-      <c r="G26" t="s">
-        <v>171</v>
-      </c>
-      <c r="H26" t="s">
-        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>70</v>
@@ -1972,19 +1981,19 @@
         <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27" t="s">
+        <v>172</v>
+      </c>
+      <c r="H27" t="s">
         <v>173</v>
-      </c>
-      <c r="F27" t="s">
-        <v>173</v>
-      </c>
-      <c r="G27" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" t="s">
-        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>70</v>
@@ -2007,19 +2016,19 @@
         <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
         <v>175</v>
-      </c>
-      <c r="F28" t="s">
-        <v>175</v>
-      </c>
-      <c r="G28" t="s">
-        <v>175</v>
-      </c>
-      <c r="H28" t="s">
-        <v>176</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>70</v>
@@ -2042,7 +2051,7 @@
         <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>97</v>
@@ -2085,19 +2094,19 @@
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>70</v>
@@ -2126,19 +2135,19 @@
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" t="s">
         <v>179</v>
-      </c>
-      <c r="F31" t="s">
-        <v>179</v>
-      </c>
-      <c r="G31" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" t="s">
-        <v>180</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>70</v>
@@ -2161,19 +2170,19 @@
         <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32" t="s">
         <v>181</v>
-      </c>
-      <c r="F32" t="s">
-        <v>181</v>
-      </c>
-      <c r="G32" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" t="s">
-        <v>182</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>70</v>
@@ -2196,19 +2205,19 @@
         <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" t="s">
+        <v>182</v>
+      </c>
+      <c r="H33" t="s">
         <v>183</v>
-      </c>
-      <c r="F33" t="s">
-        <v>183</v>
-      </c>
-      <c r="G33" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" t="s">
-        <v>184</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>70</v>
@@ -2231,19 +2240,19 @@
         <v>83</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" t="s">
         <v>185</v>
-      </c>
-      <c r="F34" t="s">
-        <v>185</v>
-      </c>
-      <c r="G34" t="s">
-        <v>185</v>
-      </c>
-      <c r="H34" t="s">
-        <v>186</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>70</v>
@@ -2266,19 +2275,19 @@
         <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35" t="s">
+        <v>186</v>
+      </c>
+      <c r="F35" t="s">
+        <v>186</v>
+      </c>
+      <c r="G35" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" t="s">
         <v>187</v>
-      </c>
-      <c r="F35" t="s">
-        <v>187</v>
-      </c>
-      <c r="G35" t="s">
-        <v>187</v>
-      </c>
-      <c r="H35" t="s">
-        <v>188</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>70</v>
@@ -2301,19 +2310,19 @@
         <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s">
+        <v>188</v>
+      </c>
+      <c r="G36" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" t="s">
         <v>189</v>
-      </c>
-      <c r="F36" t="s">
-        <v>189</v>
-      </c>
-      <c r="G36" t="s">
-        <v>189</v>
-      </c>
-      <c r="H36" t="s">
-        <v>190</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>70</v>
@@ -2336,19 +2345,19 @@
         <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37" t="s">
+        <v>190</v>
+      </c>
+      <c r="G37" t="s">
+        <v>190</v>
+      </c>
+      <c r="H37" t="s">
         <v>191</v>
-      </c>
-      <c r="F37" t="s">
-        <v>191</v>
-      </c>
-      <c r="G37" t="s">
-        <v>191</v>
-      </c>
-      <c r="H37" t="s">
-        <v>192</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>70</v>
@@ -2371,19 +2380,19 @@
         <v>87</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38" t="s">
         <v>193</v>
-      </c>
-      <c r="F38" t="s">
-        <v>193</v>
-      </c>
-      <c r="G38" t="s">
-        <v>193</v>
-      </c>
-      <c r="H38" t="s">
-        <v>194</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>70</v>
@@ -2406,19 +2415,19 @@
         <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
+        <v>194</v>
+      </c>
+      <c r="F39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G39" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" t="s">
         <v>195</v>
-      </c>
-      <c r="F39" t="s">
-        <v>195</v>
-      </c>
-      <c r="G39" t="s">
-        <v>195</v>
-      </c>
-      <c r="H39" t="s">
-        <v>196</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>70</v>
@@ -2435,13 +2444,13 @@
         <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>97</v>
@@ -2478,25 +2487,25 @@
         <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>70</v>
@@ -2525,7 +2534,7 @@
         <v>99</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -2560,7 +2569,7 @@
         <v>103</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E43" t="s">
         <v>97</v>
@@ -2589,13 +2598,13 @@
         <v>105</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>119</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E44" t="s">
         <v>97</v>
@@ -2630,7 +2639,7 @@
         <v>120</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E45" t="s">
         <v>97</v>
@@ -2659,13 +2668,13 @@
         <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E46" t="s">
         <v>97</v>
@@ -2691,51 +2700,57 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>135</v>
+        <v>211</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E47" t="s">
-        <v>97</v>
-      </c>
-      <c r="F47" t="s">
-        <v>97</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
-      </c>
-      <c r="H47" t="s">
-        <v>97</v>
+        <v>153</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J47" t="s">
-        <v>97</v>
-      </c>
-      <c r="K47" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J47" s="2">
+        <v>1</v>
+      </c>
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E48" t="s">
         <v>97</v>
@@ -2761,16 +2776,16 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E49" t="s">
         <v>97</v>
@@ -2796,16 +2811,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E50" t="s">
         <v>97</v>
@@ -2831,16 +2846,16 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E51" t="s">
         <v>97</v>
@@ -2866,16 +2881,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
         <v>97</v>
@@ -2904,34 +2919,34 @@
         <v>113</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E53" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="F53" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G53" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H53" t="s">
-        <v>203</v>
+        <v>97</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J53">
-        <v>1</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J53" t="s">
+        <v>97</v>
+      </c>
+      <c r="K53" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -2939,34 +2954,34 @@
         <v>113</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F54" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G54" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H54" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -2974,34 +2989,34 @@
         <v>113</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G55" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H55" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -3009,83 +3024,83 @@
         <v>113</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>207</v>
+      </c>
+      <c r="G56" t="s">
+        <v>207</v>
+      </c>
+      <c r="H56" t="s">
         <v>208</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56" t="s">
-        <v>211</v>
-      </c>
-      <c r="F56" t="s">
-        <v>211</v>
-      </c>
-      <c r="G56" t="s">
-        <v>211</v>
-      </c>
-      <c r="H56" t="s">
-        <v>212</v>
-      </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="F57" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H57" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J57" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J57">
+        <v>4</v>
+      </c>
+      <c r="K57">
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E58" t="s">
         <v>97</v>
@@ -3111,16 +3126,16 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s">
         <v>97</v>
@@ -3146,16 +3161,16 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E60" t="s">
         <v>97</v>
@@ -3181,36 +3196,71 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" t="s">
+        <v>97</v>
+      </c>
+      <c r="K61" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="B62" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E61" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" t="s">
-        <v>97</v>
-      </c>
-      <c r="G61" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" t="s">
-        <v>97</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J61" t="s">
-        <v>97</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="D62" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" t="s">
+        <v>97</v>
+      </c>
+      <c r="H62" t="s">
+        <v>97</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J62" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" t="s">
         <v>97</v>
       </c>
     </row>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6CB773-7E5E-4447-8173-84738E218847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468BA6DF-3E63-3C42-95AD-5DD30C41C94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="219">
   <si>
     <t>category</t>
   </si>
@@ -668,6 +668,15 @@
   </si>
   <si>
     <t>Yajur_upaakarma.pdf</t>
+  </si>
+  <si>
+    <t>Durga_saptashathi_dhyaanaatmaka_stotram</t>
+  </si>
+  <si>
+    <t>I002</t>
+  </si>
+  <si>
+    <t>Durga_saptashathi_dhyaanaatmaka_stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -2741,54 +2750,57 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="G48" t="s">
-        <v>97</v>
+        <v>216</v>
       </c>
       <c r="H48" t="s">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J48" t="s">
-        <v>97</v>
-      </c>
-      <c r="K48" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J48" s="2">
+        <v>2</v>
+      </c>
+      <c r="K48" s="2">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E49" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="F49" t="s">
         <v>97</v>
@@ -2811,16 +2823,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E50" t="s">
         <v>97</v>
@@ -2846,16 +2858,16 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E51" t="s">
         <v>97</v>
@@ -2881,16 +2893,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E52" t="s">
         <v>97</v>
@@ -2916,16 +2928,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E53" t="s">
         <v>97</v>
@@ -2957,31 +2969,31 @@
         <v>165</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="F54" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G54" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="H54" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
-      </c>
-      <c r="K54">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J54" t="s">
+        <v>97</v>
+      </c>
+      <c r="K54" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -2992,31 +3004,31 @@
         <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H55" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -3027,31 +3039,31 @@
         <v>165</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F56" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G56" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H56" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -3062,80 +3074,80 @@
         <v>165</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G57" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H57" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="H58" t="s">
-        <v>97</v>
+        <v>210</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J58" t="s">
-        <v>97</v>
-      </c>
-      <c r="K58" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J58">
+        <v>4</v>
+      </c>
+      <c r="K58">
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E59" t="s">
         <v>97</v>
@@ -3161,16 +3173,16 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E60" t="s">
         <v>97</v>
@@ -3196,16 +3208,16 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61" t="s">
         <v>97</v>
@@ -3231,36 +3243,71 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" t="s">
+        <v>97</v>
+      </c>
+      <c r="H62" t="s">
+        <v>97</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J62" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E62" t="s">
-        <v>97</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" t="s">
-        <v>97</v>
-      </c>
-      <c r="H62" t="s">
-        <v>97</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J62" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" t="s">
+      <c r="E63" t="s">
+        <v>97</v>
+      </c>
+      <c r="F63" t="s">
+        <v>97</v>
+      </c>
+      <c r="G63" t="s">
+        <v>97</v>
+      </c>
+      <c r="H63" t="s">
+        <v>97</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J63" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" t="s">
         <v>97</v>
       </c>
     </row>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468BA6DF-3E63-3C42-95AD-5DD30C41C94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851CA84-D6E5-4045-93B0-081449DA62B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="223">
   <si>
     <t>category</t>
   </si>
@@ -325,12 +325,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>TBD - Cat E</t>
-  </si>
-  <si>
-    <t>TBD - Cat F</t>
-  </si>
-  <si>
     <t>F000</t>
   </si>
   <si>
@@ -421,39 +415,6 @@
     <t>Q000</t>
   </si>
   <si>
-    <t>TBD - Cat H</t>
-  </si>
-  <si>
-    <t>TBD - Cat J</t>
-  </si>
-  <si>
-    <t>TBD - Cat K</t>
-  </si>
-  <si>
-    <t>TBD - Cat L</t>
-  </si>
-  <si>
-    <t>TBD - Cat M</t>
-  </si>
-  <si>
-    <t>TBD - Cat N</t>
-  </si>
-  <si>
-    <t>TBD - Cat P</t>
-  </si>
-  <si>
-    <t>TBD - Cat Q</t>
-  </si>
-  <si>
-    <t>TBD - Cat R</t>
-  </si>
-  <si>
-    <t>TBD - Cat S</t>
-  </si>
-  <si>
-    <t>TBD - Cat T</t>
-  </si>
-  <si>
     <t>category_folder</t>
   </si>
   <si>
@@ -616,9 +577,6 @@
     <t>Durga_saptashathi.pdf</t>
   </si>
   <si>
-    <t>TBD - Cat G</t>
-  </si>
-  <si>
     <t>O001</t>
   </si>
   <si>
@@ -677,6 +635,60 @@
   </si>
   <si>
     <t>Durga_saptashathi_dhyaanaatmaka_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Guru</t>
+  </si>
+  <si>
+    <t>Shri Lakshmi</t>
+  </si>
+  <si>
+    <t>Shri Subrahmananya</t>
+  </si>
+  <si>
+    <t>Shri Mahasaraswathi</t>
+  </si>
+  <si>
+    <t>Shri Mahaganapathi</t>
+  </si>
+  <si>
+    <t>Shri Surya</t>
+  </si>
+  <si>
+    <t>Shri Narasimhar</t>
+  </si>
+  <si>
+    <t>Shri Narayana</t>
+  </si>
+  <si>
+    <t>Parameshwaran</t>
+  </si>
+  <si>
+    <t>Shri Ayyappan</t>
+  </si>
+  <si>
+    <t>Gayathri</t>
+  </si>
+  <si>
+    <t>Shri Lalitha</t>
+  </si>
+  <si>
+    <t>Navagraham</t>
+  </si>
+  <si>
+    <t>Shri Hanuman</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>S001</t>
+  </si>
+  <si>
+    <t>Navagraha_suktham</t>
+  </si>
+  <si>
+    <t>Navagraha_suktham.pdf</t>
   </si>
 </sst>
 </file>
@@ -1048,15 +1060,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -1078,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1119,7 +1131,7 @@
         <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -1146,7 +1158,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>25</v>
@@ -1187,7 +1199,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
@@ -1222,7 +1234,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1257,7 +1269,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -1292,7 +1304,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -1327,7 +1339,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
@@ -1362,7 +1374,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
         <v>30</v>
@@ -1397,7 +1409,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
@@ -1432,7 +1444,7 @@
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -1467,7 +1479,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
@@ -1502,7 +1514,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -1537,7 +1549,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -1572,7 +1584,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
@@ -1607,7 +1619,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -1642,7 +1654,7 @@
         <v>23</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -1677,7 +1689,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
@@ -1712,7 +1724,7 @@
         <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
         <v>61</v>
@@ -1747,7 +1759,7 @@
         <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
         <v>63</v>
@@ -1782,7 +1794,7 @@
         <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
         <v>65</v>
@@ -1817,7 +1829,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -1852,7 +1864,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1879,19 +1891,19 @@
         <v>74</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>70</v>
@@ -1920,19 +1932,19 @@
         <v>75</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="F25" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="H25" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>70</v>
@@ -1955,19 +1967,19 @@
         <v>76</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="G26" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="H26" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>70</v>
@@ -1990,19 +2002,19 @@
         <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>70</v>
@@ -2025,19 +2037,19 @@
         <v>78</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>70</v>
@@ -2060,7 +2072,7 @@
         <v>96</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>97</v>
@@ -2103,19 +2115,19 @@
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>70</v>
@@ -2144,19 +2156,19 @@
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H31" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>70</v>
@@ -2179,19 +2191,19 @@
         <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F32" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G32" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>70</v>
@@ -2214,19 +2226,19 @@
         <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G33" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H33" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>70</v>
@@ -2249,19 +2261,19 @@
         <v>83</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>70</v>
@@ -2284,19 +2296,19 @@
         <v>84</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>70</v>
@@ -2319,19 +2331,19 @@
         <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="H36" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>70</v>
@@ -2354,19 +2366,19 @@
         <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F37" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>70</v>
@@ -2389,19 +2401,19 @@
         <v>87</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G38" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H38" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>70</v>
@@ -2424,19 +2436,19 @@
         <v>88</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G39" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="H39" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>70</v>
@@ -2453,13 +2465,13 @@
         <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>97</v>
@@ -2496,25 +2508,25 @@
         <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>70</v>
@@ -2537,13 +2549,13 @@
         <v>100</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
         <v>97</v>
@@ -2569,16 +2581,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E43" t="s">
         <v>97</v>
@@ -2604,16 +2616,16 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="E44" t="s">
         <v>97</v>
@@ -2639,16 +2651,16 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
         <v>97</v>
@@ -2674,16 +2686,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
         <v>97</v>
@@ -2709,28 +2721,28 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>70</v>
@@ -2750,28 +2762,28 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="F48" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="G48" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="H48" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>70</v>
@@ -2789,190 +2801,190 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F49" t="s">
+        <v>97</v>
+      </c>
+      <c r="G49" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J49" t="s">
+        <v>97</v>
+      </c>
+      <c r="K49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50" t="s">
+        <v>97</v>
+      </c>
+      <c r="G50" t="s">
+        <v>97</v>
+      </c>
+      <c r="H50" t="s">
+        <v>97</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J50" t="s">
+        <v>97</v>
+      </c>
+      <c r="K50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F49" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J49" t="s">
-        <v>97</v>
-      </c>
-      <c r="K49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
+      <c r="D51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" t="s">
+        <v>97</v>
+      </c>
+      <c r="G51" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" t="s">
+        <v>97</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J51" t="s">
+        <v>97</v>
+      </c>
+      <c r="K51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="B52" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" t="s">
-        <v>97</v>
-      </c>
-      <c r="F50" t="s">
-        <v>97</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
-      </c>
-      <c r="H50" t="s">
-        <v>97</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J50" t="s">
-        <v>97</v>
-      </c>
-      <c r="K50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
+      <c r="D52" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>97</v>
+      </c>
+      <c r="F52" t="s">
+        <v>97</v>
+      </c>
+      <c r="G52" t="s">
+        <v>97</v>
+      </c>
+      <c r="H52" t="s">
+        <v>97</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J52" t="s">
+        <v>97</v>
+      </c>
+      <c r="K52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="B53" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G51" t="s">
-        <v>97</v>
-      </c>
-      <c r="H51" t="s">
-        <v>97</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J51" t="s">
-        <v>97</v>
-      </c>
-      <c r="K51" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
+      <c r="D53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" t="s">
+        <v>97</v>
+      </c>
+      <c r="H53" t="s">
+        <v>97</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J53" t="s">
+        <v>97</v>
+      </c>
+      <c r="K53" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C52" s="2" t="s">
+      <c r="B54" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" t="s">
-        <v>97</v>
-      </c>
-      <c r="F52" t="s">
-        <v>97</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
-      </c>
-      <c r="H52" t="s">
-        <v>97</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J52" t="s">
-        <v>97</v>
-      </c>
-      <c r="K52" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E53" t="s">
-        <v>97</v>
-      </c>
-      <c r="F53" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" t="s">
-        <v>97</v>
-      </c>
-      <c r="H53" t="s">
-        <v>97</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J53" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
         <v>97</v>
@@ -2996,30 +3008,30 @@
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E55" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G55" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H55" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
@@ -3031,30 +3043,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E56" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="F56" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H56" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>70</v>
@@ -3066,30 +3078,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E57" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="F57" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="G57" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="H57" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>70</v>
@@ -3101,30 +3113,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="F58" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="G58" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="H58" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>70</v>
@@ -3136,180 +3148,262 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E59" t="s">
+        <v>97</v>
+      </c>
+      <c r="F59" t="s">
+        <v>97</v>
+      </c>
+      <c r="G59" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" t="s">
+        <v>97</v>
+      </c>
+      <c r="K59" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F60" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" t="s">
+        <v>97</v>
+      </c>
+      <c r="H60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J60" t="s">
+        <v>97</v>
+      </c>
+      <c r="K60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="B61" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E61" t="s">
+        <v>97</v>
+      </c>
+      <c r="F61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G61" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" t="s">
+        <v>97</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" t="s">
+        <v>97</v>
+      </c>
+      <c r="K61" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E59" t="s">
-        <v>97</v>
-      </c>
-      <c r="F59" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" t="s">
-        <v>97</v>
-      </c>
-      <c r="H59" t="s">
-        <v>97</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K59" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+      <c r="D62" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E62" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+      <c r="G62" t="s">
+        <v>97</v>
+      </c>
+      <c r="H62" t="s">
+        <v>97</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J62" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F60" t="s">
-        <v>97</v>
-      </c>
-      <c r="G60" t="s">
-        <v>97</v>
-      </c>
-      <c r="H60" t="s">
-        <v>97</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E63" t="s">
+        <v>221</v>
+      </c>
+      <c r="F63" t="s">
+        <v>221</v>
+      </c>
+      <c r="G63" t="s">
+        <v>221</v>
+      </c>
+      <c r="H63" t="s">
+        <v>222</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J63" s="2">
+        <v>1</v>
+      </c>
+      <c r="K63" s="2">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="B64" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E61" t="s">
-        <v>97</v>
-      </c>
-      <c r="F61" t="s">
-        <v>97</v>
-      </c>
-      <c r="G61" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" t="s">
-        <v>97</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J61" t="s">
-        <v>97</v>
-      </c>
-      <c r="K61" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" t="s">
-        <v>97</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" t="s">
-        <v>97</v>
-      </c>
-      <c r="H62" t="s">
-        <v>97</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J62" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E63" t="s">
-        <v>97</v>
-      </c>
-      <c r="F63" t="s">
-        <v>97</v>
-      </c>
-      <c r="G63" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" t="s">
-        <v>97</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J63" t="s">
-        <v>97</v>
-      </c>
-      <c r="K63" t="s">
-        <v>97</v>
-      </c>
+      <c r="D64" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" t="s">
+        <v>97</v>
+      </c>
+      <c r="F64" t="s">
+        <v>97</v>
+      </c>
+      <c r="G64" t="s">
+        <v>97</v>
+      </c>
+      <c r="H64" t="s">
+        <v>97</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J64" t="s">
+        <v>97</v>
+      </c>
+      <c r="K64" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" t="s">
+        <v>67</v>
+      </c>
+      <c r="G65" t="s">
+        <v>67</v>
+      </c>
+      <c r="H65" t="s">
+        <v>68</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J65" s="2">
+        <v>1</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0851CA84-D6E5-4045-93B0-081449DA62B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949AC48C-6CBD-3D45-8E29-DA58545D9945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="225">
   <si>
     <t>category</t>
   </si>
@@ -689,6 +689,12 @@
   </si>
   <si>
     <t>Navagraha_suktham.pdf</t>
+  </si>
+  <si>
+    <t>R001</t>
+  </si>
+  <si>
+    <t>R002</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3255,63 +3261,69 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H62" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J62" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J62" s="2">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E63" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F63" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="G63" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="H63" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>70</v>
@@ -3331,16 +3343,16 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E64" t="s">
         <v>97</v>
@@ -3366,28 +3378,28 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E65" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="F65" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="G65" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="H65" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>70</v>
@@ -3405,6 +3417,82 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
     </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" t="s">
+        <v>97</v>
+      </c>
+      <c r="F66" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" t="s">
+        <v>97</v>
+      </c>
+      <c r="H66" t="s">
+        <v>97</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J66" t="s">
+        <v>97</v>
+      </c>
+      <c r="K66" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" t="s">
+        <v>67</v>
+      </c>
+      <c r="G67" t="s">
+        <v>67</v>
+      </c>
+      <c r="H67" t="s">
+        <v>68</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J67" s="2">
+        <v>1</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949AC48C-6CBD-3D45-8E29-DA58545D9945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA40403-099A-8949-80AF-39E660573BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="246">
   <si>
     <t>category</t>
   </si>
@@ -695,6 +695,69 @@
   </si>
   <si>
     <t>R002</t>
+  </si>
+  <si>
+    <t>R003</t>
+  </si>
+  <si>
+    <t>Tripurasundari_Ashtakam_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Tripurasundari_Ashtakam_stotram</t>
+  </si>
+  <si>
+    <t>J001</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_ashtotthara_shata_naama_stotram</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_ashtotthara_shata_naama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>J002</t>
+  </si>
+  <si>
+    <t>J003</t>
+  </si>
+  <si>
+    <t>J004</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_ashtotthara_shata_naamaavali</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_ashtotthara_shata_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_Sahasranama_stotram</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_Sahasranama_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_Sahasra_naamaavali</t>
+  </si>
+  <si>
+    <t>Shri_Lakshmi_Sahasra_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>I003</t>
+  </si>
+  <si>
+    <t>I004</t>
+  </si>
+  <si>
+    <t>Aapadhunmoolana_durga_stotram</t>
+  </si>
+  <si>
+    <t>Aapadhunmoolana_durga_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Mahishaasurakrutham_Devi_Stotram</t>
+  </si>
+  <si>
+    <t>Mahishaasurakrutham_Devi_Stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -1066,15 +1129,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="39.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -2809,86 +2872,98 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="E49" t="s">
+        <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="G49" t="s">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="H49" t="s">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J49" t="s">
-        <v>97</v>
-      </c>
-      <c r="K49" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J49" s="2">
+        <v>3</v>
+      </c>
+      <c r="K49" s="2">
+        <v>3</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E50" t="s">
-        <v>97</v>
+        <v>244</v>
       </c>
       <c r="F50" t="s">
-        <v>97</v>
+        <v>244</v>
       </c>
       <c r="G50" t="s">
-        <v>97</v>
+        <v>244</v>
       </c>
       <c r="H50" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J50" t="s">
-        <v>97</v>
-      </c>
-      <c r="K50" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J50" s="2">
+        <v>4</v>
+      </c>
+      <c r="K50" s="2">
+        <v>4</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E51" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
         <v>97</v>
@@ -2911,261 +2986,261 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="F52" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="G52" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="H52" t="s">
-        <v>97</v>
+        <v>230</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J52" t="s">
-        <v>97</v>
-      </c>
-      <c r="K52" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>124</v>
+        <v>231</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>234</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>234</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>234</v>
       </c>
       <c r="H53" t="s">
-        <v>97</v>
+        <v>235</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J53" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="G54" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="H54" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J54" t="s">
-        <v>97</v>
-      </c>
-      <c r="K54" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E55" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="F55" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="G55" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="H55" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>190</v>
+        <v>121</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F56" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="G56" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="H56" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J56">
-        <v>2</v>
-      </c>
-      <c r="K56">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J56" t="s">
+        <v>97</v>
+      </c>
+      <c r="K56" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E57" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F57" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G57" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H57" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J57">
-        <v>3</v>
-      </c>
-      <c r="K57">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J57" t="s">
+        <v>97</v>
+      </c>
+      <c r="K57" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="F58" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="G58" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="H58" t="s">
-        <v>196</v>
+        <v>97</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J58">
-        <v>4</v>
-      </c>
-      <c r="K58">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J58" t="s">
+        <v>97</v>
+      </c>
+      <c r="K58" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
         <v>97</v>
@@ -3191,16 +3266,16 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E60" t="s">
         <v>97</v>
@@ -3226,209 +3301,191 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="F61" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="H61" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J61" t="s">
-        <v>97</v>
-      </c>
-      <c r="K61" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E62" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F62" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G62" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="H62" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J62" s="2">
-        <v>1</v>
-      </c>
-      <c r="K62" s="2">
-        <v>1</v>
-      </c>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" s="2"/>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62">
+        <v>2</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E63" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="F63" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="G63" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="H63" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J63" s="2">
-        <v>1</v>
-      </c>
-      <c r="K63" s="2">
-        <v>1</v>
-      </c>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" s="2"/>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
+      </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="F64" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="G64" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="H64" t="s">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J64" t="s">
-        <v>97</v>
-      </c>
-      <c r="K64" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64">
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="G65" t="s">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="H65" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J65" s="2">
-        <v>1</v>
-      </c>
-      <c r="K65" s="2">
-        <v>1</v>
-      </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J65" t="s">
+        <v>97</v>
+      </c>
+      <c r="K65" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E66" t="s">
         <v>97</v>
@@ -3454,44 +3511,313 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" t="s">
+        <v>97</v>
+      </c>
+      <c r="G67" t="s">
+        <v>97</v>
+      </c>
+      <c r="H67" t="s">
+        <v>97</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J67" t="s">
+        <v>97</v>
+      </c>
+      <c r="K67" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E68" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" t="s">
+        <v>177</v>
+      </c>
+      <c r="G68" t="s">
+        <v>177</v>
+      </c>
+      <c r="H68" t="s">
+        <v>178</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E69" t="s">
+        <v>175</v>
+      </c>
+      <c r="F69" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" t="s">
+        <v>176</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J69" s="2">
+        <v>2</v>
+      </c>
+      <c r="K69" s="2">
+        <v>2</v>
+      </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" t="s">
+        <v>227</v>
+      </c>
+      <c r="F70" t="s">
+        <v>227</v>
+      </c>
+      <c r="G70" t="s">
+        <v>227</v>
+      </c>
+      <c r="H70" t="s">
+        <v>226</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J70" s="2">
+        <v>3</v>
+      </c>
+      <c r="K70" s="2">
+        <v>3</v>
+      </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E71" t="s">
+        <v>97</v>
+      </c>
+      <c r="F71" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J71" t="s">
+        <v>97</v>
+      </c>
+      <c r="K71" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E72" t="s">
+        <v>221</v>
+      </c>
+      <c r="F72" t="s">
+        <v>221</v>
+      </c>
+      <c r="G72" t="s">
+        <v>221</v>
+      </c>
+      <c r="H72" t="s">
+        <v>222</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J72" s="2">
+        <v>1</v>
+      </c>
+      <c r="K72" s="2">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C73" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73" t="s">
+        <v>97</v>
+      </c>
+      <c r="F73" t="s">
+        <v>97</v>
+      </c>
+      <c r="G73" t="s">
+        <v>97</v>
+      </c>
+      <c r="H73" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J73" t="s">
+        <v>97</v>
+      </c>
+      <c r="K73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E74" t="s">
         <v>67</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F74" t="s">
         <v>67</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G74" t="s">
         <v>67</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H74" t="s">
         <v>68</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J67" s="2">
+      <c r="I74" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74" s="2">
         <v>1</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K74" s="2">
         <v>1</v>
       </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
-      <c r="Q67" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA40403-099A-8949-80AF-39E660573BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C710157-B562-2F4E-B032-741F808725A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="258">
   <si>
     <t>category</t>
   </si>
@@ -758,6 +758,42 @@
   </si>
   <si>
     <t>Mahishaasurakrutham_Devi_Stotram.pdf</t>
+  </si>
+  <si>
+    <t>K001</t>
+  </si>
+  <si>
+    <t>K002</t>
+  </si>
+  <si>
+    <t>K003</t>
+  </si>
+  <si>
+    <t>K004</t>
+  </si>
+  <si>
+    <t>Surya_Ashtakam</t>
+  </si>
+  <si>
+    <t>Surya_Ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Surya_mandala_ashtakam</t>
+  </si>
+  <si>
+    <t>Surya_mandala_ashtakam.pdf</t>
+  </si>
+  <si>
+    <t>Surya_mandala_stotram</t>
+  </si>
+  <si>
+    <t>Surya_mandala_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Surya_shatakam</t>
+  </si>
+  <si>
+    <t>Surya_shatakam.pdf</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3161,247 +3197,247 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>122</v>
+        <v>246</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E57" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="F57" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="G57" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="H57" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J57" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E58" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="G58" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="H58" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J58" t="s">
-        <v>97</v>
-      </c>
-      <c r="K58" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58">
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E59" t="s">
-        <v>97</v>
+        <v>254</v>
       </c>
       <c r="F59" t="s">
-        <v>97</v>
+        <v>254</v>
       </c>
       <c r="G59" t="s">
-        <v>97</v>
+        <v>254</v>
       </c>
       <c r="H59" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K59" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J59">
+        <v>3</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>125</v>
+        <v>249</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E60" t="s">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="F60" t="s">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="G60" t="s">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="H60" t="s">
-        <v>97</v>
+        <v>257</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J60">
+        <v>4</v>
+      </c>
+      <c r="K60">
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E61" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F61" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="G61" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="H61" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J61">
-        <v>1</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J61" t="s">
+        <v>97</v>
+      </c>
+      <c r="K61" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E62" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F62" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="G62" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="H62" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J62">
-        <v>2</v>
-      </c>
-      <c r="K62">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="J62" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F63" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H63" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J63">
-        <v>3</v>
-      </c>
-      <c r="K63">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J63" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
@@ -3412,273 +3448,255 @@
         <v>152</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E64" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="G64" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="H64" t="s">
-        <v>196</v>
+        <v>97</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J64">
-        <v>4</v>
-      </c>
-      <c r="K64">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J64" t="s">
+        <v>97</v>
+      </c>
+      <c r="K64" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E65" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="F65" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="G65" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="H65" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J65" t="s">
-        <v>97</v>
-      </c>
-      <c r="K65" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="F66" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="G66" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H66" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J66" t="s">
-        <v>97</v>
-      </c>
-      <c r="K66" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E67" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="F67" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="G67" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="H67" t="s">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J67" t="s">
-        <v>97</v>
-      </c>
-      <c r="K67" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="K67">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E68" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F68" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="G68" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="H68" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J68" s="2">
-        <v>1</v>
-      </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
+      <c r="J68">
+        <v>4</v>
+      </c>
+      <c r="K68">
+        <v>4</v>
+      </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E69" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H69" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J69" s="2">
-        <v>2</v>
-      </c>
-      <c r="K69" s="2">
-        <v>2</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J69" t="s">
+        <v>97</v>
+      </c>
+      <c r="K69" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E70" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="G70" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="H70" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J70" s="2">
-        <v>3</v>
-      </c>
-      <c r="K70" s="2">
-        <v>3</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J70" t="s">
+        <v>97</v>
+      </c>
+      <c r="K70" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E71" t="s">
         <v>97</v>
@@ -3704,28 +3722,28 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="F72" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="G72" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="H72" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>70</v>
@@ -3745,72 +3763,78 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>129</v>
+        <v>224</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F73" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G73" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H73" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J73" s="2">
+        <v>2</v>
+      </c>
+      <c r="K73" s="2">
+        <v>2</v>
+      </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E74" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="F74" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="G74" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="H74" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -3819,6 +3843,158 @@
       <c r="P74" s="2"/>
       <c r="Q74" s="2"/>
     </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E75" t="s">
+        <v>97</v>
+      </c>
+      <c r="F75" t="s">
+        <v>97</v>
+      </c>
+      <c r="G75" t="s">
+        <v>97</v>
+      </c>
+      <c r="H75" t="s">
+        <v>97</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J75" t="s">
+        <v>97</v>
+      </c>
+      <c r="K75" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E76" t="s">
+        <v>221</v>
+      </c>
+      <c r="F76" t="s">
+        <v>221</v>
+      </c>
+      <c r="G76" t="s">
+        <v>221</v>
+      </c>
+      <c r="H76" t="s">
+        <v>222</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J76" s="2">
+        <v>1</v>
+      </c>
+      <c r="K76" s="2">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E77" t="s">
+        <v>97</v>
+      </c>
+      <c r="F77" t="s">
+        <v>97</v>
+      </c>
+      <c r="G77" t="s">
+        <v>97</v>
+      </c>
+      <c r="H77" t="s">
+        <v>97</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J77" t="s">
+        <v>97</v>
+      </c>
+      <c r="K77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E78" t="s">
+        <v>67</v>
+      </c>
+      <c r="F78" t="s">
+        <v>67</v>
+      </c>
+      <c r="G78" t="s">
+        <v>67</v>
+      </c>
+      <c r="H78" t="s">
+        <v>68</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J78" s="2">
+        <v>1</v>
+      </c>
+      <c r="K78" s="2">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C710157-B562-2F4E-B032-741F808725A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CEA30D-6989-C34D-8F1E-E28147A85A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="264">
   <si>
     <t>category</t>
   </si>
@@ -794,6 +794,24 @@
   </si>
   <si>
     <t>Surya_shatakam.pdf</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>Q001</t>
+  </si>
+  <si>
+    <t>Shri_Hariharaputra_Ashtotthara_shata_naamaavali</t>
+  </si>
+  <si>
+    <t>Shri_Hariharaputra_Ashtotthara_shata_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>Shri_Gayathri_Stotram</t>
+  </si>
+  <si>
+    <t>Shri_Gayathri_Stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -3652,51 +3670,51 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E70" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="F70" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="G70" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="H70" t="s">
-        <v>97</v>
+        <v>261</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J70" t="s">
-        <v>97</v>
-      </c>
-      <c r="K70" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E71" t="s">
         <v>97</v>
@@ -3722,44 +3740,38 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="F72" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="G72" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="H72" t="s">
-        <v>178</v>
+        <v>263</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72">
         <v>1</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72">
         <v>1</v>
       </c>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
@@ -3769,38 +3781,32 @@
         <v>216</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="F73" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="G73" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="H73" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J73" s="2">
-        <v>2</v>
-      </c>
-      <c r="K73" s="2">
-        <v>2</v>
-      </c>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J73" t="s">
+        <v>97</v>
+      </c>
+      <c r="K73" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
@@ -3810,31 +3816,31 @@
         <v>216</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E74" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="F74" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="G74" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="H74" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J74" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K74" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -3845,72 +3851,78 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F75" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G75" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H75" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J75" t="s">
-        <v>97</v>
-      </c>
-      <c r="K75" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J75" s="2">
+        <v>2</v>
+      </c>
+      <c r="K75" s="2">
+        <v>2</v>
+      </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F76" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G76" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="H76" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J76" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K76" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -3921,16 +3933,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E77" t="s">
         <v>97</v>
@@ -3956,28 +3968,28 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E78" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="F78" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="G78" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="H78" t="s">
-        <v>68</v>
+        <v>222</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
@@ -3995,6 +4007,82 @@
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
     </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E79" t="s">
+        <v>97</v>
+      </c>
+      <c r="F79" t="s">
+        <v>97</v>
+      </c>
+      <c r="G79" t="s">
+        <v>97</v>
+      </c>
+      <c r="H79" t="s">
+        <v>97</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J79" t="s">
+        <v>97</v>
+      </c>
+      <c r="K79" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" t="s">
+        <v>67</v>
+      </c>
+      <c r="F80" t="s">
+        <v>67</v>
+      </c>
+      <c r="G80" t="s">
+        <v>67</v>
+      </c>
+      <c r="H80" t="s">
+        <v>68</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J80" s="2">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CEA30D-6989-C34D-8F1E-E28147A85A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01679A94-E9FE-554C-B3AC-FE4BFED4FD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="273">
   <si>
     <t>category</t>
   </si>
@@ -637,33 +637,18 @@
     <t>Durga_saptashathi_dhyaanaatmaka_stotram.pdf</t>
   </si>
   <si>
-    <t>Guru</t>
-  </si>
-  <si>
     <t>Shri Lakshmi</t>
   </si>
   <si>
-    <t>Shri Subrahmananya</t>
-  </si>
-  <si>
     <t>Shri Mahasaraswathi</t>
   </si>
   <si>
     <t>Shri Mahaganapathi</t>
   </si>
   <si>
-    <t>Shri Surya</t>
-  </si>
-  <si>
     <t>Shri Narasimhar</t>
   </si>
   <si>
-    <t>Shri Narayana</t>
-  </si>
-  <si>
-    <t>Parameshwaran</t>
-  </si>
-  <si>
     <t>Shri Ayyappan</t>
   </si>
   <si>
@@ -812,6 +797,48 @@
   </si>
   <si>
     <t>Shri_Gayathri_Stotram.pdf</t>
+  </si>
+  <si>
+    <t>Surya Bhagavan</t>
+  </si>
+  <si>
+    <t>Shri Gurubhyo Namah</t>
+  </si>
+  <si>
+    <t>Shri Subrahmananyar/Murugan</t>
+  </si>
+  <si>
+    <t>Om Namo Naaraayanaaya</t>
+  </si>
+  <si>
+    <t>Om Namah Shivaaya</t>
+  </si>
+  <si>
+    <t>L001</t>
+  </si>
+  <si>
+    <t>M001</t>
+  </si>
+  <si>
+    <t>N001</t>
+  </si>
+  <si>
+    <t>Shri_Narasimha_stotram</t>
+  </si>
+  <si>
+    <t>Shri_Narasimha_stotram.pdf</t>
+  </si>
+  <si>
+    <t>Achyutha_astakam</t>
+  </si>
+  <si>
+    <t>Achyutha_astakam.pdf</t>
+  </si>
+  <si>
+    <t>Arda_naarishwara_ashtotthara_naamaavali</t>
+  </si>
+  <si>
+    <t>Arda_naarishwara_ashtotthara_naamaavali.pdf</t>
   </si>
 </sst>
 </file>
@@ -1183,15 +1210,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="39.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -2672,7 +2699,7 @@
         <v>100</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>99</v>
@@ -2707,7 +2734,7 @@
         <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>101</v>
@@ -2742,7 +2769,7 @@
         <v>103</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>207</v>
+        <v>261</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>117</v>
@@ -2777,7 +2804,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>118</v>
@@ -2932,22 +2959,22 @@
         <v>197</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E49" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="G49" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H49" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>70</v>
@@ -2973,22 +3000,22 @@
         <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E50" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="F50" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G50" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H50" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>70</v>
@@ -3011,7 +3038,7 @@
         <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>120</v>
@@ -3043,25 +3070,25 @@
         <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E52" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F52" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="G52" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H52" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>70</v>
@@ -3078,25 +3105,25 @@
         <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E53" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F53" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G53" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H53" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>70</v>
@@ -3113,25 +3140,25 @@
         <v>106</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E54" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F54" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G54" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H54" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
@@ -3148,25 +3175,25 @@
         <v>106</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E55" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F55" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G55" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H55" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>70</v>
@@ -3183,7 +3210,7 @@
         <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>121</v>
@@ -3218,25 +3245,25 @@
         <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E57" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F57" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G57" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H57" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>70</v>
@@ -3253,25 +3280,25 @@
         <v>107</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E58" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F58" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G58" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H58" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>70</v>
@@ -3288,25 +3315,25 @@
         <v>107</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E59" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F59" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G59" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H59" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
@@ -3323,25 +3350,25 @@
         <v>107</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E60" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F60" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G60" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H60" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>70</v>
@@ -3358,7 +3385,7 @@
         <v>108</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>122</v>
@@ -3390,51 +3417,51 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E62" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="F62" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="G62" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="H62" t="s">
-        <v>97</v>
+        <v>268</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J62" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E63" t="s">
         <v>97</v>
@@ -3460,107 +3487,107 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="F64" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="G64" t="s">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="H64" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J64" t="s">
-        <v>97</v>
-      </c>
-      <c r="K64" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E65" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="F65" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="G65" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="H65" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J65" t="s">
+        <v>97</v>
+      </c>
+      <c r="K65" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E66" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="F66" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="G66" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="H66" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
@@ -3571,31 +3598,31 @@
         <v>152</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E67" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="F67" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G67" t="s">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="H67" t="s">
-        <v>194</v>
+        <v>97</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J67">
-        <v>3</v>
-      </c>
-      <c r="K67">
-        <v>3</v>
+        <v>97</v>
+      </c>
+      <c r="J67" t="s">
+        <v>97</v>
+      </c>
+      <c r="K67" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
@@ -3606,399 +3633,387 @@
         <v>152</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E68" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F68" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G68" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H68" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E69" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="F69" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="G69" t="s">
-        <v>97</v>
+        <v>188</v>
       </c>
       <c r="H69" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J69" t="s">
-        <v>97</v>
-      </c>
-      <c r="K69" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>258</v>
+        <v>191</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E70" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="F70" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="G70" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="H70" t="s">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K70">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="G71" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="H71" t="s">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J71" t="s">
-        <v>97</v>
-      </c>
-      <c r="K71" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71">
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>259</v>
+        <v>126</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" t="s">
-        <v>262</v>
+        <v>97</v>
       </c>
       <c r="F72" t="s">
-        <v>262</v>
+        <v>97</v>
       </c>
       <c r="G72" t="s">
-        <v>262</v>
+        <v>97</v>
       </c>
       <c r="H72" t="s">
-        <v>263</v>
+        <v>97</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="J72" t="s">
+        <v>97</v>
+      </c>
+      <c r="K72" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
       <c r="F73" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
       <c r="G73" t="s">
-        <v>97</v>
+        <v>255</v>
       </c>
       <c r="H73" t="s">
-        <v>97</v>
+        <v>256</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E74" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="G74" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="H74" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J74" s="2">
-        <v>1</v>
-      </c>
-      <c r="K74" s="2">
-        <v>1</v>
-      </c>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J74" t="s">
+        <v>97</v>
+      </c>
+      <c r="K74" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E75" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="F75" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="G75" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="H75" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J75" s="2">
-        <v>2</v>
-      </c>
-      <c r="K75" s="2">
-        <v>2</v>
-      </c>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="F76" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="H76" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J76" s="2">
-        <v>3</v>
-      </c>
-      <c r="K76" s="2">
-        <v>3</v>
-      </c>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J76" t="s">
+        <v>97</v>
+      </c>
+      <c r="K76" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>128</v>
+        <v>218</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="F77" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="G77" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="H77" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J77" t="s">
-        <v>97</v>
-      </c>
-      <c r="K77" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J77" s="2">
+        <v>1</v>
+      </c>
+      <c r="K77" s="2">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E78" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="F78" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="G78" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="H78" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J78" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -4009,79 +4024,196 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="F79" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="G79" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="H79" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J79" t="s">
-        <v>97</v>
-      </c>
-      <c r="K79" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J79" s="2">
+        <v>3</v>
+      </c>
+      <c r="K79" s="2">
+        <v>3</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E80" t="s">
+        <v>97</v>
+      </c>
+      <c r="F80" t="s">
+        <v>97</v>
+      </c>
+      <c r="G80" t="s">
+        <v>97</v>
+      </c>
+      <c r="H80" t="s">
+        <v>97</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J80" t="s">
+        <v>97</v>
+      </c>
+      <c r="K80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E81" t="s">
+        <v>216</v>
+      </c>
+      <c r="F81" t="s">
+        <v>216</v>
+      </c>
+      <c r="G81" t="s">
+        <v>216</v>
+      </c>
+      <c r="H81" t="s">
+        <v>217</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J81" s="2">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="2"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D80" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E82" t="s">
+        <v>97</v>
+      </c>
+      <c r="F82" t="s">
+        <v>97</v>
+      </c>
+      <c r="G82" t="s">
+        <v>97</v>
+      </c>
+      <c r="H82" t="s">
+        <v>97</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J82" t="s">
+        <v>97</v>
+      </c>
+      <c r="K82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E83" t="s">
         <v>67</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F83" t="s">
         <v>67</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G83" t="s">
         <v>67</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H83" t="s">
         <v>68</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="I83" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J83" s="2">
         <v>1</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K83" s="2">
         <v>1</v>
       </c>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01679A94-E9FE-554C-B3AC-FE4BFED4FD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A3DA33-45C1-EF4C-904D-537CF1FCF116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="278">
   <si>
     <t>category</t>
   </si>
@@ -839,6 +839,21 @@
   </si>
   <si>
     <t>Arda_naarishwara_ashtotthara_naamaavali.pdf</t>
+  </si>
+  <si>
+    <t>H001</t>
+  </si>
+  <si>
+    <t>G001</t>
+  </si>
+  <si>
+    <t>F001</t>
+  </si>
+  <si>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>Dakshinaamoorthy_Stotram</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -2731,51 +2746,57 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" t="s">
-        <v>97</v>
-      </c>
-      <c r="F43" t="s">
-        <v>97</v>
-      </c>
-      <c r="G43" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" t="s">
-        <v>97</v>
+        <v>136</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J43" t="s">
-        <v>97</v>
-      </c>
-      <c r="K43" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
         <v>97</v>
@@ -2801,51 +2822,57 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E45" t="s">
-        <v>97</v>
-      </c>
-      <c r="F45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G45" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" t="s">
-        <v>97</v>
+        <v>137</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J45" t="s">
-        <v>97</v>
-      </c>
-      <c r="K45" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J45" s="2">
+        <v>1</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
         <v>97</v>
@@ -2871,28 +2898,28 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>70</v>
@@ -2912,78 +2939,72 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E48" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="H48" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J48" s="2">
-        <v>2</v>
-      </c>
-      <c r="K48" s="2">
-        <v>2</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J48" t="s">
+        <v>97</v>
+      </c>
+      <c r="K48" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F49" t="s">
-        <v>237</v>
-      </c>
-      <c r="G49" t="s">
-        <v>237</v>
-      </c>
-      <c r="H49" t="s">
-        <v>238</v>
+        <v>139</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J49" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -3000,175 +3021,196 @@
         <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E50" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="F50" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="H50" t="s">
-        <v>240</v>
+        <v>97</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J50" s="2">
-        <v>4</v>
-      </c>
-      <c r="K50" s="2">
-        <v>4</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="J50" t="s">
+        <v>97</v>
+      </c>
+      <c r="K50" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G51" t="s">
-        <v>97</v>
-      </c>
-      <c r="H51" t="s">
-        <v>97</v>
+        <v>140</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J51" t="s">
-        <v>97</v>
-      </c>
-      <c r="K51" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+      <c r="K51" s="2">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E52" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="F52" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="G52" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="H52" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J52">
-        <v>1</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
+      <c r="J52" s="2">
+        <v>2</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E53" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G53" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H53" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J53">
-        <v>2</v>
-      </c>
-      <c r="K53">
-        <v>2</v>
-      </c>
+      <c r="J53" s="2">
+        <v>3</v>
+      </c>
+      <c r="K53" s="2">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E54" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F54" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G54" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="H54" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J54">
-        <v>3</v>
-      </c>
-      <c r="K54">
-        <v>3</v>
-      </c>
+      <c r="J54" s="2">
+        <v>4</v>
+      </c>
+      <c r="K54" s="2">
+        <v>4</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
@@ -3178,171 +3220,168 @@
         <v>205</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E55" t="s">
-        <v>233</v>
-      </c>
       <c r="F55" t="s">
-        <v>233</v>
+        <v>97</v>
       </c>
       <c r="G55" t="s">
-        <v>233</v>
+        <v>97</v>
       </c>
       <c r="H55" t="s">
-        <v>234</v>
+        <v>97</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J55">
-        <v>4</v>
-      </c>
-      <c r="K55">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J55" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>121</v>
+        <v>223</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E56" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="F56" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="G56" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="H56" t="s">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" t="s">
-        <v>97</v>
-      </c>
-      <c r="K56" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E57" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F57" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="G57" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="H57" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E58" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F58" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="G58" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="H58" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E59" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F59" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="G59" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="H59" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
@@ -3353,185 +3392,185 @@
         <v>259</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>244</v>
+        <v>121</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>142</v>
       </c>
       <c r="E60" t="s">
-        <v>251</v>
+        <v>97</v>
       </c>
       <c r="F60" t="s">
-        <v>251</v>
+        <v>97</v>
       </c>
       <c r="G60" t="s">
-        <v>251</v>
+        <v>97</v>
       </c>
       <c r="H60" t="s">
-        <v>252</v>
+        <v>97</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J60">
-        <v>4</v>
-      </c>
-      <c r="K60">
-        <v>4</v>
+        <v>97</v>
+      </c>
+      <c r="J60" t="s">
+        <v>97</v>
+      </c>
+      <c r="K60" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E61" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="F61" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="G61" t="s">
-        <v>97</v>
+        <v>245</v>
       </c>
       <c r="H61" t="s">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J61" t="s">
-        <v>97</v>
-      </c>
-      <c r="K61" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E62" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F62" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="G62" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="H62" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="G63" t="s">
-        <v>97</v>
+        <v>249</v>
       </c>
       <c r="H63" t="s">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J63" t="s">
-        <v>97</v>
-      </c>
-      <c r="K63" t="s">
-        <v>97</v>
+        <v>70</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F64" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="G64" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="H64" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E65" t="s">
         <v>97</v>
@@ -3555,30 +3594,30 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E66" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F66" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G66" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H66" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>70</v>
@@ -3590,18 +3629,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E67" t="s">
         <v>97</v>
@@ -3625,30 +3664,30 @@
         <v>97</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="F68" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="G68" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="H68" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>70</v>
@@ -3660,77 +3699,77 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E69" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F69" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="G69" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="H69" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J69">
-        <v>2</v>
-      </c>
-      <c r="K69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+      <c r="J69" t="s">
+        <v>97</v>
+      </c>
+      <c r="K69" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>191</v>
+        <v>266</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="F70" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="G70" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="H70" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>111</v>
       </c>
@@ -3738,343 +3777,325 @@
         <v>152</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>146</v>
       </c>
       <c r="E71" t="s">
+        <v>97</v>
+      </c>
+      <c r="F71" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" t="s">
+        <v>97</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J71" t="s">
+        <v>97</v>
+      </c>
+      <c r="K71" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E72" t="s">
+        <v>186</v>
+      </c>
+      <c r="F72" t="s">
+        <v>186</v>
+      </c>
+      <c r="G72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H72" t="s">
+        <v>187</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" t="s">
+        <v>188</v>
+      </c>
+      <c r="F73" t="s">
+        <v>188</v>
+      </c>
+      <c r="G73" t="s">
+        <v>188</v>
+      </c>
+      <c r="H73" t="s">
+        <v>189</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E74" t="s">
+        <v>193</v>
+      </c>
+      <c r="F74" t="s">
+        <v>193</v>
+      </c>
+      <c r="G74" t="s">
+        <v>193</v>
+      </c>
+      <c r="H74" t="s">
+        <v>194</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E75" t="s">
         <v>195</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F75" t="s">
         <v>195</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G75" t="s">
         <v>195</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H75" t="s">
         <v>196</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J71">
+      <c r="I75" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J75">
         <v>4</v>
       </c>
-      <c r="K71">
+      <c r="K75">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72" s="2" t="s">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E72" t="s">
-        <v>97</v>
-      </c>
-      <c r="F72" t="s">
-        <v>97</v>
-      </c>
-      <c r="G72" t="s">
-        <v>97</v>
-      </c>
-      <c r="H72" t="s">
-        <v>97</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J72" t="s">
-        <v>97</v>
-      </c>
-      <c r="K72" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A73" s="2" t="s">
+      <c r="E76" t="s">
+        <v>97</v>
+      </c>
+      <c r="F76" t="s">
+        <v>97</v>
+      </c>
+      <c r="G76" t="s">
+        <v>97</v>
+      </c>
+      <c r="H76" t="s">
+        <v>97</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J76" t="s">
+        <v>97</v>
+      </c>
+      <c r="K76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E77" t="s">
         <v>255</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F77" t="s">
         <v>255</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G77" t="s">
         <v>255</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H77" t="s">
         <v>256</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J73">
+      <c r="I77" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J77">
         <v>1</v>
       </c>
-      <c r="K73">
+      <c r="K77">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74" s="2" t="s">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E74" t="s">
-        <v>97</v>
-      </c>
-      <c r="F74" t="s">
-        <v>97</v>
-      </c>
-      <c r="G74" t="s">
-        <v>97</v>
-      </c>
-      <c r="H74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J74" t="s">
-        <v>97</v>
-      </c>
-      <c r="K74" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A75" s="2" t="s">
+      <c r="E78" t="s">
+        <v>97</v>
+      </c>
+      <c r="F78" t="s">
+        <v>97</v>
+      </c>
+      <c r="G78" t="s">
+        <v>97</v>
+      </c>
+      <c r="H78" t="s">
+        <v>97</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J78" t="s">
+        <v>97</v>
+      </c>
+      <c r="K78" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E79" t="s">
         <v>257</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F79" t="s">
         <v>257</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G79" t="s">
         <v>257</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H79" t="s">
         <v>258</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J75">
+      <c r="I79" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J79">
         <v>1</v>
       </c>
-      <c r="K75">
+      <c r="K79">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A76" s="2" t="s">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="E76" t="s">
-        <v>97</v>
-      </c>
-      <c r="F76" t="s">
-        <v>97</v>
-      </c>
-      <c r="G76" t="s">
-        <v>97</v>
-      </c>
-      <c r="H76" t="s">
-        <v>97</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J76" t="s">
-        <v>97</v>
-      </c>
-      <c r="K76" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E77" t="s">
-        <v>177</v>
-      </c>
-      <c r="F77" t="s">
-        <v>177</v>
-      </c>
-      <c r="G77" t="s">
-        <v>177</v>
-      </c>
-      <c r="H77" t="s">
-        <v>178</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J77" s="2">
-        <v>1</v>
-      </c>
-      <c r="K77" s="2">
-        <v>1</v>
-      </c>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E78" t="s">
-        <v>175</v>
-      </c>
-      <c r="F78" t="s">
-        <v>175</v>
-      </c>
-      <c r="G78" t="s">
-        <v>175</v>
-      </c>
-      <c r="H78" t="s">
-        <v>176</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J78" s="2">
-        <v>2</v>
-      </c>
-      <c r="K78" s="2">
-        <v>2</v>
-      </c>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E79" t="s">
-        <v>222</v>
-      </c>
-      <c r="F79" t="s">
-        <v>222</v>
-      </c>
-      <c r="G79" t="s">
-        <v>222</v>
-      </c>
-      <c r="H79" t="s">
-        <v>221</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J79" s="2">
-        <v>3</v>
-      </c>
-      <c r="K79" s="2">
-        <v>3</v>
-      </c>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A80" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E80" t="s">
         <v>97</v>
@@ -4100,28 +4121,28 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E81" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="F81" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="G81" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="H81" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>70</v>
@@ -4141,72 +4162,78 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E82" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="F82" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G82" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="H82" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J82" t="s">
-        <v>97</v>
-      </c>
-      <c r="K82" t="s">
-        <v>97</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="J82" s="2">
+        <v>2</v>
+      </c>
+      <c r="K82" s="2">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="2"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="F83" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="G83" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="H83" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J83" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K83" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -4215,6 +4242,158 @@
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
     </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84" t="s">
+        <v>97</v>
+      </c>
+      <c r="F84" t="s">
+        <v>97</v>
+      </c>
+      <c r="G84" t="s">
+        <v>97</v>
+      </c>
+      <c r="H84" t="s">
+        <v>97</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J84" t="s">
+        <v>97</v>
+      </c>
+      <c r="K84" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E85" t="s">
+        <v>216</v>
+      </c>
+      <c r="F85" t="s">
+        <v>216</v>
+      </c>
+      <c r="G85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H85" t="s">
+        <v>217</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J85" s="2">
+        <v>1</v>
+      </c>
+      <c r="K85" s="2">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="2"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" t="s">
+        <v>97</v>
+      </c>
+      <c r="F86" t="s">
+        <v>97</v>
+      </c>
+      <c r="G86" t="s">
+        <v>97</v>
+      </c>
+      <c r="H86" t="s">
+        <v>97</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J86" t="s">
+        <v>97</v>
+      </c>
+      <c r="K86" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" t="s">
+        <v>67</v>
+      </c>
+      <c r="G87" t="s">
+        <v>67</v>
+      </c>
+      <c r="H87" t="s">
+        <v>68</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J87" s="2">
+        <v>1</v>
+      </c>
+      <c r="K87" s="2">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/configuration_doc.xlsx
+++ b/configuration_doc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashokkrishnamoorthy/Documents/sangrahaalaya/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A3DA33-45C1-EF4C-904D-537CF1FCF116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9491AFE6-315B-F946-BA1B-C8F4D5DE62FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20480" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="279">
   <si>
     <t>category</t>
   </si>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>Dakshinaamoorthy_Stotram</t>
+  </si>
+  <si>
+    <t>Dakshinaamoorthy_Stotram.pdf</t>
   </si>
 </sst>
 </file>
@@ -2919,7 +2922,7 @@
         <v>157</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>70</v>
@@ -2995,7 +2998,7 @@
         <v>277</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>70</v>
